--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5432-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5432-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFF6F63E-D639-4F9D-B64F-935A2E0B8B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1344DDA3-5548-46B4-8C33-F633F1D53475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{559D8824-1E6D-44F2-8D3F-2D178A56E02B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{37039324-000A-48F2-AB7B-F25426B75F4B}"/>
   </bookViews>
   <sheets>
     <sheet name="5432-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1469,27 +1469,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904A7849-B34E-4CF1-B72A-90CED0A4C198}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68C651B-25A7-473E-95EA-97327B3AFB07}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1679,7 +1679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2021</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2020</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2019</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2018</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2017</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2016</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2015</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2014</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2013</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2012</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2011</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2010</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2009</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2008</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2007</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2006</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2005</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2004</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2003</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2002</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2001</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2000</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>1999</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1998</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>1997</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>44</v>
       </c>
